--- a/Datos/MunicipiosPDET.xlsx
+++ b/Datos/MunicipiosPDET.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mc-c2\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniandes-my.sharepoint.com/personal/mc_caraballo_uniandes_edu_co/Documents/Universidad/MECA/Big Data y Machine Learning/Repositorios/BD_ML_taller_1/Trabajo-Final--Evaluaci-n-de-impacto/Datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54382C6E-F02B-4C53-916F-88CC07F3A244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MunicipiosPDET" sheetId="1" r:id="rId1"/>
@@ -1504,16 +1504,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E171"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="45.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" style="2" customWidth="1"/>
-    <col min="3" max="3" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.26953125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24" style="1" customWidth="1"/>
-    <col min="5" max="5" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>200</v>
       </c>
@@ -1530,7 +1530,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -1564,7 +1564,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -1581,7 +1581,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -1598,7 +1598,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -1615,7 +1615,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -1632,7 +1632,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -1649,7 +1649,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -1666,7 +1666,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -1683,7 +1683,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -1700,7 +1700,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>0</v>
       </c>
@@ -1717,7 +1717,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -1734,7 +1734,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>0</v>
       </c>
@@ -1768,7 +1768,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>0</v>
       </c>
@@ -1785,7 +1785,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>0</v>
       </c>
@@ -1802,7 +1802,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>0</v>
       </c>
@@ -1819,7 +1819,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>0</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>0</v>
       </c>
@@ -1853,7 +1853,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>0</v>
       </c>
@@ -1870,7 +1870,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>0</v>
       </c>
@@ -1887,7 +1887,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>0</v>
       </c>
@@ -1904,7 +1904,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>0</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>0</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -1955,7 +1955,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -1972,7 +1972,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>28</v>
       </c>
@@ -1989,7 +1989,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -2006,7 +2006,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -2023,7 +2023,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>33</v>
       </c>
@@ -2040,7 +2040,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -2057,7 +2057,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>33</v>
       </c>
@@ -2074,7 +2074,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>33</v>
       </c>
@@ -2091,7 +2091,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -2108,7 +2108,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>33</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>33</v>
       </c>
@@ -2142,7 +2142,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>33</v>
       </c>
@@ -2159,7 +2159,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>33</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>33</v>
       </c>
@@ -2193,7 +2193,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>33</v>
       </c>
@@ -2210,7 +2210,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>33</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>48</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>48</v>
       </c>
@@ -2261,7 +2261,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>48</v>
       </c>
@@ -2278,7 +2278,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>48</v>
       </c>
@@ -2295,7 +2295,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>48</v>
       </c>
@@ -2312,7 +2312,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>48</v>
       </c>
@@ -2329,7 +2329,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>48</v>
       </c>
@@ -2346,7 +2346,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>48</v>
       </c>
@@ -2363,7 +2363,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>58</v>
       </c>
@@ -2380,7 +2380,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>58</v>
       </c>
@@ -2397,7 +2397,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>58</v>
       </c>
@@ -2414,7 +2414,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>58</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>58</v>
       </c>
@@ -2448,7 +2448,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>58</v>
       </c>
@@ -2465,7 +2465,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>58</v>
       </c>
@@ -2482,7 +2482,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>58</v>
       </c>
@@ -2499,7 +2499,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>58</v>
       </c>
@@ -2516,7 +2516,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>58</v>
       </c>
@@ -2533,7 +2533,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>58</v>
       </c>
@@ -2550,7 +2550,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>58</v>
       </c>
@@ -2567,7 +2567,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>58</v>
       </c>
@@ -2584,7 +2584,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>58</v>
       </c>
@@ -2601,7 +2601,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>73</v>
       </c>
@@ -2618,7 +2618,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>73</v>
       </c>
@@ -2635,7 +2635,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>73</v>
       </c>
@@ -2652,7 +2652,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>73</v>
       </c>
@@ -2669,7 +2669,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>73</v>
       </c>
@@ -2686,7 +2686,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>73</v>
       </c>
@@ -2703,7 +2703,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>73</v>
       </c>
@@ -2720,7 +2720,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>73</v>
       </c>
@@ -2737,7 +2737,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>73</v>
       </c>
@@ -2754,7 +2754,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>73</v>
       </c>
@@ -2771,7 +2771,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>73</v>
       </c>
@@ -2788,7 +2788,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>73</v>
       </c>
@@ -2805,7 +2805,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>73</v>
       </c>
@@ -2822,7 +2822,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>73</v>
       </c>
@@ -2839,7 +2839,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>73</v>
       </c>
@@ -2856,7 +2856,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>73</v>
       </c>
@@ -2873,7 +2873,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>73</v>
       </c>
@@ -2890,7 +2890,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>93</v>
       </c>
@@ -2907,7 +2907,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>93</v>
       </c>
@@ -2924,7 +2924,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>93</v>
       </c>
@@ -2941,7 +2941,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>93</v>
       </c>
@@ -2958,7 +2958,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>93</v>
       </c>
@@ -2975,7 +2975,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>93</v>
       </c>
@@ -2992,7 +2992,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>93</v>
       </c>
@@ -3009,7 +3009,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>93</v>
       </c>
@@ -3026,7 +3026,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>93</v>
       </c>
@@ -3043,7 +3043,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>93</v>
       </c>
@@ -3060,7 +3060,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>93</v>
       </c>
@@ -3077,7 +3077,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>93</v>
       </c>
@@ -3094,7 +3094,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>107</v>
       </c>
@@ -3111,7 +3111,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>107</v>
       </c>
@@ -3128,7 +3128,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>107</v>
       </c>
@@ -3145,7 +3145,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>107</v>
       </c>
@@ -3162,7 +3162,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>107</v>
       </c>
@@ -3179,7 +3179,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>107</v>
       </c>
@@ -3196,7 +3196,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>107</v>
       </c>
@@ -3213,7 +3213,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>107</v>
       </c>
@@ -3230,7 +3230,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>107</v>
       </c>
@@ -3247,7 +3247,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>107</v>
       </c>
@@ -3264,7 +3264,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>107</v>
       </c>
@@ -3281,7 +3281,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>107</v>
       </c>
@@ -3298,7 +3298,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>107</v>
       </c>
@@ -3315,7 +3315,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>107</v>
       </c>
@@ -3332,7 +3332,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>107</v>
       </c>
@@ -3349,7 +3349,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>125</v>
       </c>
@@ -3366,7 +3366,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>125</v>
       </c>
@@ -3383,7 +3383,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>125</v>
       </c>
@@ -3400,7 +3400,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>125</v>
       </c>
@@ -3417,7 +3417,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>130</v>
       </c>
@@ -3434,7 +3434,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>130</v>
       </c>
@@ -3451,7 +3451,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>130</v>
       </c>
@@ -3468,7 +3468,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>130</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>130</v>
       </c>
@@ -3502,7 +3502,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>130</v>
       </c>
@@ -3519,7 +3519,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>130</v>
       </c>
@@ -3536,7 +3536,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>130</v>
       </c>
@@ -3553,7 +3553,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>130</v>
       </c>
@@ -3570,7 +3570,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>130</v>
       </c>
@@ -3587,7 +3587,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>130</v>
       </c>
@@ -3604,7 +3604,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>142</v>
       </c>
@@ -3621,7 +3621,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>142</v>
       </c>
@@ -3638,7 +3638,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>142</v>
       </c>
@@ -3655,7 +3655,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>142</v>
       </c>
@@ -3672,7 +3672,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>142</v>
       </c>
@@ -3689,7 +3689,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>142</v>
       </c>
@@ -3706,7 +3706,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>142</v>
       </c>
@@ -3723,7 +3723,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>142</v>
       </c>
@@ -3740,7 +3740,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>142</v>
       </c>
@@ -3757,7 +3757,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>152</v>
       </c>
@@ -3774,7 +3774,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>152</v>
       </c>
@@ -3791,7 +3791,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>152</v>
       </c>
@@ -3808,7 +3808,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>152</v>
       </c>
@@ -3825,7 +3825,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>152</v>
       </c>
@@ -3842,7 +3842,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>152</v>
       </c>
@@ -3859,7 +3859,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>152</v>
       </c>
@@ -3876,7 +3876,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>152</v>
       </c>
@@ -3893,7 +3893,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>152</v>
       </c>
@@ -3910,7 +3910,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>152</v>
       </c>
@@ -3927,7 +3927,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>152</v>
       </c>
@@ -3944,7 +3944,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>152</v>
       </c>
@@ -3961,7 +3961,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>152</v>
       </c>
@@ -3978,7 +3978,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>152</v>
       </c>
@@ -3995,7 +3995,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>152</v>
       </c>
@@ -4012,7 +4012,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>171</v>
       </c>
@@ -4029,7 +4029,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>171</v>
       </c>
@@ -4046,7 +4046,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>171</v>
       </c>
@@ -4063,7 +4063,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>171</v>
       </c>
@@ -4080,7 +4080,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>171</v>
       </c>
@@ -4097,7 +4097,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>171</v>
       </c>
@@ -4114,7 +4114,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>171</v>
       </c>
@@ -4131,7 +4131,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>178</v>
       </c>
@@ -4148,7 +4148,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>178</v>
       </c>
@@ -4165,7 +4165,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>178</v>
       </c>
@@ -4182,7 +4182,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>178</v>
       </c>
@@ -4199,7 +4199,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>178</v>
       </c>
@@ -4216,7 +4216,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>184</v>
       </c>
@@ -4233,7 +4233,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>184</v>
       </c>
@@ -4250,7 +4250,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>184</v>
       </c>
@@ -4267,7 +4267,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>184</v>
       </c>
@@ -4284,7 +4284,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>190</v>
       </c>
@@ -4301,7 +4301,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>190</v>
       </c>
@@ -4318,7 +4318,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>190</v>
       </c>
@@ -4335,7 +4335,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>190</v>
       </c>
@@ -4352,7 +4352,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>190</v>
       </c>
@@ -4369,7 +4369,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>190</v>
       </c>
@@ -4386,7 +4386,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>190</v>
       </c>
@@ -4403,7 +4403,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>190</v>
       </c>
@@ -4432,9 +4432,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F171"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>199</v>
       </c>
@@ -4454,7 +4454,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4474,7 +4474,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -4494,7 +4494,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1</v>
       </c>
@@ -4514,7 +4514,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1</v>
       </c>
@@ -4534,7 +4534,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1</v>
       </c>
@@ -4554,7 +4554,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1</v>
       </c>
@@ -4574,7 +4574,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1</v>
       </c>
@@ -4594,7 +4594,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1</v>
       </c>
@@ -4614,7 +4614,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>1</v>
       </c>
@@ -4634,7 +4634,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1</v>
       </c>
@@ -4654,7 +4654,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>1</v>
       </c>
@@ -4674,7 +4674,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1</v>
       </c>
@@ -4694,7 +4694,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>1</v>
       </c>
@@ -4714,7 +4714,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>1</v>
       </c>
@@ -4734,7 +4734,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1</v>
       </c>
@@ -4754,7 +4754,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1</v>
       </c>
@@ -4774,7 +4774,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>1</v>
       </c>
@@ -4794,7 +4794,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1</v>
       </c>
@@ -4814,7 +4814,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>1</v>
       </c>
@@ -4834,7 +4834,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>1</v>
       </c>
@@ -4854,7 +4854,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>1</v>
       </c>
@@ -4874,7 +4874,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>1</v>
       </c>
@@ -4894,7 +4894,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>1</v>
       </c>
@@ -4914,7 +4914,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>1</v>
       </c>
@@ -4934,7 +4934,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>2</v>
       </c>
@@ -4954,7 +4954,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2</v>
       </c>
@@ -4974,7 +4974,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>2</v>
       </c>
@@ -4994,7 +4994,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>2</v>
       </c>
@@ -5014,7 +5014,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>3</v>
       </c>
@@ -5034,7 +5034,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>3</v>
       </c>
@@ -5054,7 +5054,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>3</v>
       </c>
@@ -5074,7 +5074,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>3</v>
       </c>
@@ -5094,7 +5094,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>3</v>
       </c>
@@ -5114,7 +5114,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>3</v>
       </c>
@@ -5134,7 +5134,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>3</v>
       </c>
@@ -5154,7 +5154,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>3</v>
       </c>
@@ -5174,7 +5174,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>3</v>
       </c>
@@ -5194,7 +5194,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>3</v>
       </c>
@@ -5214,7 +5214,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>3</v>
       </c>
@@ -5234,7 +5234,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>3</v>
       </c>
@@ -5254,7 +5254,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>3</v>
       </c>
@@ -5274,7 +5274,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>4</v>
       </c>
@@ -5294,7 +5294,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>4</v>
       </c>
@@ -5314,7 +5314,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>4</v>
       </c>
@@ -5334,7 +5334,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>4</v>
       </c>
@@ -5354,7 +5354,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>4</v>
       </c>
@@ -5374,7 +5374,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>4</v>
       </c>
@@ -5394,7 +5394,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>4</v>
       </c>
@@ -5414,7 +5414,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>4</v>
       </c>
@@ -5434,7 +5434,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>5</v>
       </c>
@@ -5454,7 +5454,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>5</v>
       </c>
@@ -5474,7 +5474,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>5</v>
       </c>
@@ -5494,7 +5494,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>5</v>
       </c>
@@ -5514,7 +5514,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>5</v>
       </c>
@@ -5534,7 +5534,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>5</v>
       </c>
@@ -5554,7 +5554,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>5</v>
       </c>
@@ -5574,7 +5574,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>5</v>
       </c>
@@ -5594,7 +5594,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>5</v>
       </c>
@@ -5614,7 +5614,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>5</v>
       </c>
@@ -5634,7 +5634,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>5</v>
       </c>
@@ -5654,7 +5654,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>5</v>
       </c>
@@ -5674,7 +5674,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>5</v>
       </c>
@@ -5694,7 +5694,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>5</v>
       </c>
@@ -5714,7 +5714,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>6</v>
       </c>
@@ -5734,7 +5734,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>6</v>
       </c>
@@ -5754,7 +5754,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>6</v>
       </c>
@@ -5774,7 +5774,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>6</v>
       </c>
@@ -5794,7 +5794,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>6</v>
       </c>
@@ -5814,7 +5814,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>6</v>
       </c>
@@ -5834,7 +5834,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>6</v>
       </c>
@@ -5854,7 +5854,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>6</v>
       </c>
@@ -5874,7 +5874,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>6</v>
       </c>
@@ -5894,7 +5894,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>6</v>
       </c>
@@ -5914,7 +5914,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>6</v>
       </c>
@@ -5934,7 +5934,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>6</v>
       </c>
@@ -5954,7 +5954,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>6</v>
       </c>
@@ -5974,7 +5974,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>6</v>
       </c>
@@ -5994,7 +5994,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>6</v>
       </c>
@@ -6014,7 +6014,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>6</v>
       </c>
@@ -6034,7 +6034,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>6</v>
       </c>
@@ -6054,7 +6054,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>7</v>
       </c>
@@ -6074,7 +6074,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>7</v>
       </c>
@@ -6094,7 +6094,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>7</v>
       </c>
@@ -6114,7 +6114,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>7</v>
       </c>
@@ -6134,7 +6134,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>7</v>
       </c>
@@ -6154,7 +6154,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>7</v>
       </c>
@@ -6174,7 +6174,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>7</v>
       </c>
@@ -6194,7 +6194,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>7</v>
       </c>
@@ -6214,7 +6214,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>7</v>
       </c>
@@ -6234,7 +6234,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>7</v>
       </c>
@@ -6254,7 +6254,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>7</v>
       </c>
@@ -6274,7 +6274,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>7</v>
       </c>
@@ -6294,7 +6294,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>8</v>
       </c>
@@ -6314,7 +6314,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>8</v>
       </c>
@@ -6334,7 +6334,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>8</v>
       </c>
@@ -6354,7 +6354,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>8</v>
       </c>
@@ -6374,7 +6374,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>8</v>
       </c>
@@ -6394,7 +6394,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>8</v>
       </c>
@@ -6414,7 +6414,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>8</v>
       </c>
@@ -6434,7 +6434,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>8</v>
       </c>
@@ -6454,7 +6454,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>8</v>
       </c>
@@ -6474,7 +6474,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>8</v>
       </c>
@@ -6494,7 +6494,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>8</v>
       </c>
@@ -6514,7 +6514,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>8</v>
       </c>
@@ -6534,7 +6534,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>8</v>
       </c>
@@ -6554,7 +6554,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>8</v>
       </c>
@@ -6574,7 +6574,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>8</v>
       </c>
@@ -6594,7 +6594,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>9</v>
       </c>
@@ -6614,7 +6614,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>9</v>
       </c>
@@ -6634,7 +6634,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>9</v>
       </c>
@@ -6654,7 +6654,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>9</v>
       </c>
@@ -6674,7 +6674,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>10</v>
       </c>
@@ -6694,7 +6694,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>10</v>
       </c>
@@ -6714,7 +6714,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>10</v>
       </c>
@@ -6734,7 +6734,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>10</v>
       </c>
@@ -6754,7 +6754,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>10</v>
       </c>
@@ -6774,7 +6774,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>10</v>
       </c>
@@ -6794,7 +6794,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>10</v>
       </c>
@@ -6814,7 +6814,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>10</v>
       </c>
@@ -6834,7 +6834,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>10</v>
       </c>
@@ -6854,7 +6854,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>10</v>
       </c>
@@ -6874,7 +6874,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>10</v>
       </c>
@@ -6894,7 +6894,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>11</v>
       </c>
@@ -6914,7 +6914,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>11</v>
       </c>
@@ -6934,7 +6934,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>11</v>
       </c>
@@ -6954,7 +6954,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>11</v>
       </c>
@@ -6974,7 +6974,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>11</v>
       </c>
@@ -6994,7 +6994,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>11</v>
       </c>
@@ -7014,7 +7014,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>11</v>
       </c>
@@ -7034,7 +7034,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>11</v>
       </c>
@@ -7054,7 +7054,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>11</v>
       </c>
@@ -7074,7 +7074,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>12</v>
       </c>
@@ -7094,7 +7094,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>12</v>
       </c>
@@ -7114,7 +7114,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>12</v>
       </c>
@@ -7134,7 +7134,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>12</v>
       </c>
@@ -7154,7 +7154,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>12</v>
       </c>
@@ -7174,7 +7174,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>12</v>
       </c>
@@ -7194,7 +7194,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>12</v>
       </c>
@@ -7214,7 +7214,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>12</v>
       </c>
@@ -7234,7 +7234,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>12</v>
       </c>
@@ -7254,7 +7254,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>12</v>
       </c>
@@ -7274,7 +7274,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>12</v>
       </c>
@@ -7294,7 +7294,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>12</v>
       </c>
@@ -7314,7 +7314,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>12</v>
       </c>
@@ -7334,7 +7334,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>12</v>
       </c>
@@ -7354,7 +7354,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>12</v>
       </c>
@@ -7374,7 +7374,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>13</v>
       </c>
@@ -7394,7 +7394,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>13</v>
       </c>
@@ -7414,7 +7414,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>13</v>
       </c>
@@ -7434,7 +7434,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>13</v>
       </c>
@@ -7454,7 +7454,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>13</v>
       </c>
@@ -7474,7 +7474,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>13</v>
       </c>
@@ -7494,7 +7494,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>13</v>
       </c>
@@ -7514,7 +7514,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>14</v>
       </c>
@@ -7534,7 +7534,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>14</v>
       </c>
@@ -7554,7 +7554,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>14</v>
       </c>
@@ -7574,7 +7574,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>14</v>
       </c>
@@ -7594,7 +7594,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>14</v>
       </c>
@@ -7614,7 +7614,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>15</v>
       </c>
@@ -7634,7 +7634,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>15</v>
       </c>
@@ -7654,7 +7654,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>15</v>
       </c>
@@ -7674,7 +7674,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>15</v>
       </c>
@@ -7694,7 +7694,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>16</v>
       </c>
@@ -7714,7 +7714,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>16</v>
       </c>
@@ -7734,7 +7734,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>16</v>
       </c>
@@ -7754,7 +7754,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>16</v>
       </c>
@@ -7774,7 +7774,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>16</v>
       </c>
@@ -7794,7 +7794,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>16</v>
       </c>
@@ -7814,7 +7814,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>16</v>
       </c>
@@ -7834,7 +7834,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>16</v>
       </c>
